--- a/04_DESIGN_TABLES/DesignTable_5404.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5404.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:X37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -595,6 +595,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2731,24 +2736,76 @@
           <t>5404-16-04</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.21363</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.23863</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.47739</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.49163</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.281</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>5404-16-04</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1-11 1/2</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1/4-18</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-16-04 column 'L LGTH' = 1.960 (catalog_verified.json); OMi Items row 1283: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-16-04 column 'C HEX' = 1.375 (catalog_verified.json); OMi Items row 1283: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-16-04 column 'A1 DRILL' = 0.938 (catalog_verified.json); OMi Items row 1283: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-16-04 column 'A2 DRILL' = 0.281 (catalog_verified.json); OMi Items row 1283: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[16] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[4] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -2759,6 +2816,11 @@
       <c r="W28" t="inlineStr">
         <is>
           <t>5404-16-04</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2768,24 +2830,76 @@
           <t>5404-20-12</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.55713</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.58338</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.96768</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.98887</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.719</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>5404-20-12</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>3/4-14</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-20-12 column 'L LGTH' = 2.260 (catalog_verified.json); OMi Items row 1288: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-20-12 column 'C HEX' = 1.750 (catalog_verified.json); OMi Items row 1288: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-20-12 column 'A1 DRILL' = 1.250 (catalog_verified.json); OMi Items row 1288: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-20-12 column 'A2 DRILL' = 0.719 (catalog_verified.json); OMi Items row 1288: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[20] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[12] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12] thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -2796,6 +2910,11 @@
       <c r="W29" t="inlineStr">
         <is>
           <t>5404-20-12</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2805,24 +2924,76 @@
           <t>5404-24-12</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.79609</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.82234</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.96768</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.98887</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.719</v>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>5404-24-12</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>3/4-14</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-24-12 column 'L LGTH' = 2.380 (catalog_verified.json); OMi Items row 1291: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-24-12 column 'C HEX' = 2.000 (catalog_verified.json); OMi Items row 1291: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-24-12 column 'A1 DRILL' = 1.500 (catalog_verified.json); OMi Items row 1291: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-24-12 column 'A2 DRILL' = 0.719 (catalog_verified.json); OMi Items row 1291: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[24] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[12] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12] thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -2833,6 +3004,11 @@
       <c r="W30" t="inlineStr">
         <is>
           <t>5404-24-12</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2842,24 +3018,76 @@
           <t>5404-32-12</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.26902</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.29627</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.96768</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.98887</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.719</v>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>5404-32-12</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2-11 1/2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>3/4-14</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-12 column 'L LGTH' = 2.540 (catalog_verified.json); OMi Items row 1295: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-12 column 'C HEX' = 2.500 (catalog_verified.json); OMi Items row 1295: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-12 column 'A1 DRILL' = 1.938 (catalog_verified.json); OMi Items row 1295: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-12 column 'A2 DRILL' = 0.719 (catalog_verified.json); OMi Items row 1295: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[32] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[12] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 3/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[12] thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -2870,6 +3098,11 @@
       <c r="W31" t="inlineStr">
         <is>
           <t>5404-32-12</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2879,24 +3112,76 @@
           <t>5404-32-16</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.26902</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.29627</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.21363</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.23863</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.6828</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.9379999999999999</v>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>5404-32-16</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2-11 1/2</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1-11 1/2</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-16 column 'L LGTH' = 2.630 (catalog_verified.json); OMi Items row 1296: no dimension; no Air-Way row; equals the 2026-10-02 proposal; HEXB@HEX: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-16 column 'C HEX' = 2.500 (catalog_verified.json); OMi Items row 1296: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-16 column 'A1 DRILL' = 1.938 (catalog_verified.json); OMi Items row 1296: no dimension; no Air-Way row; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p11 table TFA-p011-t04 (MP-MP HEX NIPPLE) row 5404-32-16 column 'A2 DRILL' = 0.938 (catalog_verified.json); OMi Items row 1296: no dimension; no Air-Way row; equals the 2026-10-02 proposal; NPTFA_ENDL@DRIVE: gen_straight2 ENDL[32] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFA_E0@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; NPTFA_E1@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; NPTFA_L2@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; PIPEODA@DRIVE: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32]; equals the 2026-10-02 proposal; $PRP@EndA_Thread: ASME B1.20.1 / B1.20.3 2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[32] thread text; equals the 2026-10-02 proposal; NPTFB_ENDL@DRIVE: gen_straight2 ENDL[16] (male NPTF end length, Brennan-measured, from the built 5404 rows of the base table); equals the 2026-10-02 proposal; NPTFB_E0@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; NPTFB_E1@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; NPTFB_L2@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; PIPEODB@DRIVE: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16]; equals the 2026-10-02 proposal; $PRP@EndB_Thread: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16] thread text; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): body sizes from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -2907,6 +3192,11 @@
       <c r="W32" t="inlineStr">
         <is>
           <t>5404-32-16</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2916,24 +3206,58 @@
           <t>5404-40-40</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.515</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.318</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.318</v>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>5404-40-40</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2 1/2-8</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>2 1/2-8</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex / bores from the Brennan TFA catalog p11 alone; the -40 NPTF ends are not in the end library</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -2944,6 +3268,11 @@
       <c r="W33" t="inlineStr">
         <is>
           <t>5404-40-40</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
